--- a/LISTAS_ORDENADAS/MI/Sogas Varillas Cables/SOGA REVESTIDA.xlsx
+++ b/LISTAS_ORDENADAS/MI/Sogas Varillas Cables/SOGA REVESTIDA.xlsx
@@ -912,16 +912,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45203.55242617083</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>
       <c r="G1" s="25" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="F6" s="29" t="n"/>
     </row>
@@ -935,7 +931,6 @@
     <row r="8" ht="22.5" customHeight="1" s="35">
       <c r="A8" s="1" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="35">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -1066,7 +1061,7 @@
     <row r="19" ht="54" customHeight="1" s="35">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">
+          <t>
 </t>
         </is>
       </c>
@@ -1088,16 +1083,6 @@
       <c r="D22" s="9" t="n"/>
       <c r="F22" s="26" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="33.75" customHeight="1" s="35">
       <c r="A33" s="34" t="inlineStr">
         <is>
@@ -1145,7 +1130,9 @@
         </is>
       </c>
       <c r="C36" s="32" t="n"/>
-      <c r="D36" s="27" t="n"/>
+      <c r="D36" s="27" t="n">
+        <v>31.973</v>
+      </c>
     </row>
     <row r="37" ht="39" customHeight="1" s="35">
       <c r="A37" s="12" t="inlineStr">
@@ -1163,10 +1150,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
